--- a/modelado/modelos/resultados/Class/ML_cla.xlsx
+++ b/modelado/modelos/resultados/Class/ML_cla.xlsx
@@ -9,6 +9,8 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="RandomForestClassifier_SQA" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ExtraTreesClassifier_SQA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="RandomForestClassifier_HKP" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ExtraTreesClassifier_HKP" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -199,6 +201,128 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8096250" cy="2990850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6296025" cy="4667250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8096250" cy="2990850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6296025" cy="4667250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -941,4 +1065,420 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>f1-score</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8924731182795699</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8236641221374046</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.546875</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3580562659846547</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4327666151468315</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.5604395604395604</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5610561056105611</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5607476635514018</v>
+      </c>
+      <c r="E5" t="n">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6862222222222222</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6862222222222222</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6862222222222222</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6862222222222222</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>macro avg</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6240068142641672</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6038618299582619</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6057261336118792</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>weighted avg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6666628353264382</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6862222222222222</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6686610473474893</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>IoU</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Class 0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.700194678780013</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Class 1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2761341222879685</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Class 2</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.3896103896103896</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Cohen's Kappa</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Aggregated R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0.4568464783495108</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.7606555223464966</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>f1-score</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7721198988804623</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8842018196856907</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8243686138422981</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5163636363636364</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3631713554987212</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4264264264264264</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.543046357615894</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5412541254125413</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5421487603305785</v>
+      </c>
+      <c r="E5" t="n">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6791111111111111</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6791111111111111</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6791111111111111</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6791111111111111</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>macro avg</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6105099642866643</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5962091001989843</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.597647933533101</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>weighted avg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6591799111156335</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6791111111111111</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6636299399131935</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>IoU</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Class 0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7012135126270909</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Class 1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2709923664122137</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Class 2</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.3718820861678004</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Cohen's Kappa</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Aggregated R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0.4476030025301618</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.767038881778717</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/modelado/modelos/resultados/Class/ML_cla.xlsx
+++ b/modelado/modelos/resultados/Class/ML_cla.xlsx
@@ -223,9 +223,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -251,9 +248,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -345,6 +339,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -370,6 +367,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7833948339483395</v>
+        <v>0.8252091145082203</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8779983457402812</v>
+        <v>0.9417379855167873</v>
       </c>
       <c r="D3" t="n">
-        <v>0.828003120124805</v>
+        <v>0.8796310530361261</v>
       </c>
       <c r="E3" t="n">
-        <v>2418</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="4">
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7836538461538461</v>
+        <v>0.7137176938369781</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6810584958217271</v>
+        <v>0.4911080711354309</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7287630402384501</v>
+        <v>0.5818476499189628</v>
       </c>
       <c r="E4" t="n">
-        <v>1436</v>
+        <v>731</v>
       </c>
     </row>
     <row r="5">
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6974169741697417</v>
+        <v>0.7490566037735849</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5851393188854489</v>
+        <v>0.5430916552667578</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6296590007930214</v>
       </c>
       <c r="E5" t="n">
-        <v>646</v>
+        <v>731</v>
       </c>
     </row>
     <row r="6">
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7731111111111111</v>
+        <v>0.8037777777777778</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7731111111111111</v>
+        <v>0.8037777777777778</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7731111111111111</v>
+        <v>0.8037777777777778</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7731111111111111</v>
+        <v>0.8037777777777778</v>
       </c>
     </row>
     <row r="7">
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.754821884757309</v>
+        <v>0.7626611373729277</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7147320534824857</v>
+        <v>0.6586459039729921</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7310432655756305</v>
+        <v>0.69704590124937</v>
       </c>
       <c r="E7" t="n">
         <v>4500</v>
@@ -784,13 +784,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7711348881950358</v>
+        <v>0.794727400317621</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7731111111111111</v>
+        <v>0.8037777777777778</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7688235954078004</v>
+        <v>0.7906512223987137</v>
       </c>
       <c r="E8" t="n">
         <v>4500</v>
@@ -806,31 +806,31 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Class 0</t>
+          <t>Clase 0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7064891846921797</v>
+        <v>0.785126234906696</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>Clase 1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5732708089097304</v>
+        <v>0.4102857142857143</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Clase 2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4594907407407408</v>
       </c>
     </row>
     <row r="16">
@@ -841,16 +841,16 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Aggregated R2</t>
+          <t>Agg R2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.6023785456635072</v>
+        <v>0.5566344656198398</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4463035464286804</v>
+        <v>0.6422488689422607</v>
       </c>
     </row>
   </sheetData>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7860621955788685</v>
+        <v>0.8331339712918661</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8676592224979321</v>
+        <v>0.9170506912442397</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8248476508747788</v>
+        <v>0.8730805390159825</v>
       </c>
       <c r="E3" t="n">
-        <v>2418</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="4">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7578304048892284</v>
+        <v>0.6556836902800659</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6908077994428969</v>
+        <v>0.5444596443228454</v>
       </c>
       <c r="D4" t="n">
-        <v>0.722768670309654</v>
+        <v>0.5949177877428998</v>
       </c>
       <c r="E4" t="n">
-        <v>1436</v>
+        <v>731</v>
       </c>
     </row>
     <row r="5">
@@ -935,16 +935,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6877394636015326</v>
+        <v>0.7122040072859745</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5557275541795665</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6147260273972602</v>
+        <v>0.6109375</v>
       </c>
       <c r="E5" t="n">
-        <v>646</v>
+        <v>731</v>
       </c>
     </row>
     <row r="6">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7664444444444445</v>
+        <v>0.7944444444444444</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7664444444444445</v>
+        <v>0.7944444444444444</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7664444444444445</v>
+        <v>0.7944444444444444</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7664444444444445</v>
+        <v>0.7944444444444444</v>
       </c>
     </row>
     <row r="7">
@@ -973,13 +973,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7438773546898765</v>
+        <v>0.7336738896193022</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7047315253734651</v>
+        <v>0.6654646854991059</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7207807828605644</v>
+        <v>0.6929786089196274</v>
       </c>
       <c r="E7" t="n">
         <v>4500</v>
@@ -992,13 +992,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7629383430704947</v>
+        <v>0.78466375815677</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7664444444444445</v>
+        <v>0.7944444444444444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7621089875730019</v>
+        <v>0.7853108650823588</v>
       </c>
       <c r="E8" t="n">
         <v>4500</v>
@@ -1014,31 +1014,31 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Class 0</t>
+          <t>Clase 0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7019069923051188</v>
+        <v>0.7747497219132369</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>Clase 1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5658870507701084</v>
+        <v>0.4234042553191489</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Clase 2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4437577255871446</v>
+        <v>0.4398200224971879</v>
       </c>
     </row>
     <row r="16">
@@ -1049,16 +1049,16 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Aggregated R2</t>
+          <t>Agg R2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.5915599241482002</v>
+        <v>0.549800062557512</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4273653030395508</v>
+        <v>0.662808358669281</v>
       </c>
     </row>
   </sheetData>

--- a/modelado/modelos/resultados/Class/ML_cla.xlsx
+++ b/modelado/modelos/resultados/Class/ML_cla.xlsx
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8252091145082203</v>
+        <v>0.8636748518204911</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9417379855167873</v>
+        <v>0.9392265193370166</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8796310530361261</v>
+        <v>0.8998676665196295</v>
       </c>
       <c r="E3" t="n">
-        <v>3038</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="4">
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7137176938369781</v>
+        <v>0.6792452830188679</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4911080711354309</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5818476499189628</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="E4" t="n">
-        <v>731</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5">
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7490566037735849</v>
+        <v>0.69375</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5430916552667578</v>
+        <v>0.5362318840579711</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6296590007930214</v>
+        <v>0.6049046321525886</v>
       </c>
       <c r="E5" t="n">
-        <v>731</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6">
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8037777777777778</v>
+        <v>0.826</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8037777777777778</v>
+        <v>0.826</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8037777777777778</v>
+        <v>0.826</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8037777777777778</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="7">
@@ -765,16 +765,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7626611373729277</v>
+        <v>0.7455567116131196</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6586459039729921</v>
+        <v>0.6657325112765902</v>
       </c>
       <c r="D7" t="n">
-        <v>0.69704590124937</v>
+        <v>0.6983120776994826</v>
       </c>
       <c r="E7" t="n">
-        <v>4500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="8">
@@ -784,16 +784,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.794727400317621</v>
+        <v>0.8147739417746392</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8037777777777778</v>
+        <v>0.826</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7906512223987137</v>
+        <v>0.8164236527480886</v>
       </c>
       <c r="E8" t="n">
-        <v>4500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.785126234906696</v>
+        <v>0.8179631114675221</v>
       </c>
     </row>
     <row r="12">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4102857142857143</v>
+        <v>0.4186046511627907</v>
       </c>
     </row>
     <row r="13">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4594907407407408</v>
+        <v>0.43359375</v>
       </c>
     </row>
     <row r="16">
@@ -847,10 +847,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.5566344656198398</v>
+        <v>0.5656760975414937</v>
       </c>
       <c r="B17" t="n">
-        <v>0.6422488689422607</v>
+        <v>0.7799260020256042</v>
       </c>
     </row>
   </sheetData>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8331339712918661</v>
+        <v>0.8677474402730375</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9170506912442397</v>
+        <v>0.9364640883977901</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8730805390159825</v>
+        <v>0.9007971656333038</v>
       </c>
       <c r="E3" t="n">
-        <v>3038</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="4">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6556836902800659</v>
+        <v>0.69375</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5444596443228454</v>
+        <v>0.5362318840579711</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5949177877428998</v>
+        <v>0.6049046321525886</v>
       </c>
       <c r="E4" t="n">
-        <v>731</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5">
@@ -935,16 +935,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7122040072859745</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5507246376811594</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6109375</v>
+        <v>0.608</v>
       </c>
       <c r="E5" t="n">
-        <v>731</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7944444444444444</v>
+        <v>0.828</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7944444444444444</v>
+        <v>0.828</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7944444444444444</v>
+        <v>0.828</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7944444444444444</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="7">
@@ -973,16 +973,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7336738896193022</v>
+        <v>0.7466896229481553</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6654646854991059</v>
+        <v>0.6744735367123068</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6929786089196274</v>
+        <v>0.7045672659286307</v>
       </c>
       <c r="E7" t="n">
-        <v>4500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="8">
@@ -992,16 +992,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.78466375815677</v>
+        <v>0.8176295039005363</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7944444444444444</v>
+        <v>0.828</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7853108650823588</v>
+        <v>0.8195579871555692</v>
       </c>
       <c r="E8" t="n">
-        <v>4500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7747497219132369</v>
+        <v>0.8195004029008863</v>
       </c>
     </row>
     <row r="12">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4234042553191489</v>
+        <v>0.43359375</v>
       </c>
     </row>
     <row r="13">
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4398200224971879</v>
+        <v>0.4367816091954023</v>
       </c>
     </row>
     <row r="16">
@@ -1055,10 +1055,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.549800062557512</v>
+        <v>0.5744035050675675</v>
       </c>
       <c r="B17" t="n">
-        <v>0.662808358669281</v>
+        <v>0.8039767742156982</v>
       </c>
     </row>
   </sheetData>

--- a/modelado/modelos/resultados/Class/ML_cla.xlsx
+++ b/modelado/modelos/resultados/Class/ML_cla.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="1" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,22 +11,33 @@
     <sheet name="ExtraTreesClassifier_SQA" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="RandomForestClassifier_HKP" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="ExtraTreesClassifier_HKP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="RandomForestClassifier_HKP_VAL" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ExtraTreesClassifier_HKP_VAL" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="RandomForestClassifier_SQA_VAL" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ExtraTreesClassifier_SQA_VAL" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -40,12 +51,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -58,11 +84,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -176,7 +207,7 @@
       <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6296025" cy="4667250"/>
+    <ext cx="6210300" cy="4667250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -223,6 +254,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -234,7 +268,65 @@
       <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6296025" cy="4667250"/>
+    <ext cx="6210300" cy="4667250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8096250" cy="2990850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6210300" cy="4667250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -255,7 +347,68 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8096250" cy="2990850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6210300" cy="4667250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -316,7 +469,129 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8096250" cy="2990850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6296025" cy="4667250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8096250" cy="2990850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6296025" cy="4667250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -645,7 +920,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -657,189 +932,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E17"/>
+  <dimension ref="A2:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8636748518204911</v>
+        <v>0.7733905579399142</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9392265193370166</v>
+        <v>0.9751082251082251</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8998676665196295</v>
+        <v>0.8626136907611297</v>
       </c>
       <c r="E3" t="n">
-        <v>1086</v>
+        <v>924</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6792452830188679</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5901639344262295</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="E4" t="n">
-        <v>207</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.69375</v>
+        <v>0.8622754491017964</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5362318840579711</v>
+        <v>0.5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6049046321525886</v>
+        <v>0.6329670329670329</v>
       </c>
       <c r="E5" t="n">
-        <v>207</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.826</v>
+        <v>0.7846666666666666</v>
       </c>
       <c r="C6" t="n">
-        <v>0.826</v>
+        <v>0.7846666666666666</v>
       </c>
       <c r="D6" t="n">
-        <v>0.826</v>
+        <v>0.7846666666666666</v>
       </c>
       <c r="E6" t="n">
-        <v>0.826</v>
+        <v>0.7846666666666666</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>macro avg</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7455567116131196</v>
+        <v>0.8071267642519988</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6657325112765902</v>
+        <v>0.6444805194805195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6983120776994826</v>
+        <v>0.6915093640497384</v>
       </c>
       <c r="E7" t="n">
         <v>1500</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>weighted avg</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8147739417746392</v>
+        <v>0.7928226127756749</v>
       </c>
       <c r="C8" t="n">
-        <v>0.826</v>
+        <v>0.7846666666666666</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8164236527480886</v>
+        <v>0.7640575985753684</v>
       </c>
       <c r="E8" t="n">
         <v>1500</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>IoU</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Clase 0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8179631114675221</v>
+        <v>0.7584175084175084</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Clase 1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4186046511627907</v>
+        <v>0.4074074074074074</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Clase 2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.43359375</v>
+        <v>0.4630225080385852</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Cohen's Kappa</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Agg R2</t>
         </is>
@@ -847,10 +1122,112 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.5656760975414937</v>
+        <v>0.550164336248677</v>
       </c>
       <c r="B17" t="n">
-        <v>0.7799260020256042</v>
+        <v>0.1964746117591858</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Importance</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.2071227206725126</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MLOTST</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.1463407042172171</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.1313302884376739</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SPM</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.1256028916785747</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.1226589887357535</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>VGO</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.1070804347232021</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>UGO</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.1033584709731902</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MSEN</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.02981336864283028</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MCOS</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.02669213191904563</v>
       </c>
     </row>
   </sheetData>
@@ -869,185 +1246,185 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8677474402730375</v>
+        <v>0.7664670658682635</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9364640883977901</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9007971656333038</v>
+        <v>0.8561872909698997</v>
       </c>
       <c r="E3" t="n">
-        <v>1086</v>
+        <v>924</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.69375</v>
+        <v>0.7607361963190185</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5362318840579711</v>
+        <v>0.4305555555555556</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6049046321525886</v>
+        <v>0.5498891352549889</v>
       </c>
       <c r="E4" t="n">
-        <v>207</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.8511904761904762</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5507246376811594</v>
+        <v>0.4965277777777778</v>
       </c>
       <c r="D5" t="n">
-        <v>0.608</v>
+        <v>0.6271929824561403</v>
       </c>
       <c r="E5" t="n">
-        <v>207</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.828</v>
+        <v>0.7753333333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>0.828</v>
+        <v>0.7753333333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>0.828</v>
+        <v>0.7753333333333333</v>
       </c>
       <c r="E6" t="n">
-        <v>0.828</v>
+        <v>0.7753333333333333</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>macro avg</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7466896229481553</v>
+        <v>0.792797912792586</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6744735367123068</v>
+        <v>0.6322601010101011</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7045672659286307</v>
+        <v>0.677756469560343</v>
       </c>
       <c r="E7" t="n">
         <v>1500</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>weighted avg</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8176295039005363</v>
+        <v>0.7816336336966733</v>
       </c>
       <c r="C8" t="n">
-        <v>0.828</v>
+        <v>0.7753333333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8195579871555692</v>
+        <v>0.753411137837995</v>
       </c>
       <c r="E8" t="n">
         <v>1500</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>IoU</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Clase 0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8195004029008863</v>
+        <v>0.7485380116959064</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Clase 1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.43359375</v>
+        <v>0.3792048929663608</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Clase 2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4367816091954023</v>
+        <v>0.4568690095846645</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Cohen's Kappa</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Agg R2</t>
         </is>
@@ -1055,10 +1432,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.5744035050675675</v>
+        <v>0.5295556324894184</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8039767742156982</v>
+        <v>0.1638491153717041</v>
       </c>
     </row>
   </sheetData>
@@ -1073,200 +1450,302 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E17"/>
+  <dimension ref="A2:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.7639311043566362</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8924731182795699</v>
+        <v>0.9308641975308642</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8236641221374046</v>
+        <v>0.8391764051196439</v>
       </c>
       <c r="E3" t="n">
-        <v>2418</v>
+        <v>810</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.546875</v>
+        <v>0.5914634146341463</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3580562659846547</v>
+        <v>0.2811594202898551</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4327666151468315</v>
+        <v>0.381139489194499</v>
       </c>
       <c r="E4" t="n">
-        <v>1173</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5604395604395604</v>
+        <v>0.5816618911174785</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5610561056105611</v>
+        <v>0.5884057971014492</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5607476635514018</v>
+        <v>0.5850144092219021</v>
       </c>
       <c r="E5" t="n">
-        <v>909</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6862222222222222</v>
+        <v>0.7026666666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6862222222222222</v>
+        <v>0.7026666666666667</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6862222222222222</v>
+        <v>0.7026666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6862222222222222</v>
+        <v>0.7026666666666667</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>macro avg</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6240068142641672</v>
+        <v>0.645685470036087</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6038618299582619</v>
+        <v>0.6001431383073895</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6057261336118792</v>
+        <v>0.6017767678453484</v>
       </c>
       <c r="E7" t="n">
-        <v>4500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>weighted avg</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6666628353264382</v>
+        <v>0.6823416166754572</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6862222222222222</v>
+        <v>0.7026666666666667</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6686610473474893</v>
+        <v>0.6753706554003799</v>
       </c>
       <c r="E8" t="n">
-        <v>4500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>IoU</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Class 0</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Clase 0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.700194678780013</v>
+        <v>0.7229146692233941</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Class 1</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Clase 1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2761341222879685</v>
+        <v>0.2354368932038835</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Class 2</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Clase 2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3896103896103896</v>
+        <v>0.4134419551934827</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Cohen's Kappa</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>Aggregated R2</t>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Agg R2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.4568464783495108</v>
+        <v>0.4746946515435261</v>
       </c>
       <c r="B17" t="n">
-        <v>0.7606555223464966</v>
+        <v>0.7354341149330139</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Importance</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.204248916608479</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MLOTST</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.1495863029490745</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.1267514691377882</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SPM</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.1229888892995561</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.1165877172142335</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>VGO</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.1140705087201506</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>UGO</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.1120572452483879</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MSEN</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.02731703898404229</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MCOS</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.026391911838288</v>
       </c>
     </row>
   </sheetData>
@@ -1285,196 +1764,1028 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7721198988804623</v>
+        <v>0.7507447864945382</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8842018196856907</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8243686138422981</v>
+        <v>0.8321408915795266</v>
       </c>
       <c r="E3" t="n">
-        <v>2418</v>
+        <v>810</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5163636363636364</v>
+        <v>0.5695364238410596</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3631713554987212</v>
+        <v>0.2492753623188406</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4264264264264264</v>
+        <v>0.3467741935483871</v>
       </c>
       <c r="E4" t="n">
-        <v>1173</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.543046357615894</v>
+        <v>0.5906432748538012</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5412541254125413</v>
+        <v>0.5855072463768116</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5421487603305785</v>
+        <v>0.5880640465793304</v>
       </c>
       <c r="E5" t="n">
-        <v>909</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6791111111111111</v>
+        <v>0.696</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6791111111111111</v>
+        <v>0.696</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6791111111111111</v>
+        <v>0.696</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6791111111111111</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>macro avg</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6105099642866643</v>
+        <v>0.6369748283964664</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5962091001989843</v>
+        <v>0.5893719806763286</v>
       </c>
       <c r="D7" t="n">
-        <v>0.597647933533101</v>
+        <v>0.5889930439024148</v>
       </c>
       <c r="E7" t="n">
-        <v>4500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>weighted avg</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6591799111156335</v>
+        <v>0.6722435154068687</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6791111111111111</v>
+        <v>0.696</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6636299399131935</v>
+        <v>0.6643688766823195</v>
       </c>
       <c r="E8" t="n">
-        <v>4500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>IoU</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Class 0</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Clase 0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7012135126270909</v>
+        <v>0.7125353440150801</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Class 1</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Clase 1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2709923664122137</v>
+        <v>0.2097560975609756</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Class 2</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Clase 2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3718820861678004</v>
+        <v>0.4164948453608248</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Cohen's Kappa</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>Aggregated R2</t>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Agg R2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.4476030025301618</v>
+        <v>0.4589656277066549</v>
       </c>
       <c r="B17" t="n">
-        <v>0.767038881778717</v>
+        <v>0.6735662221908569</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>f1-score</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7613967022308439</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9235294117647059</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.834662413609782</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6112759643916914</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3169230769230769</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4174265450861195</v>
+      </c>
+      <c r="E4" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.6439267886855241</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5953846153846154</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.6187050359712231</v>
+      </c>
+      <c r="E5" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.721</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>macro avg</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6721998184360198</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6119457013574661</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6235979982223748</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>weighted avg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.7034187277642081</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6974705436079672</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IoU</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Clase 0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7162408759124088</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Clase 1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.263764404609475</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Clase 2</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4479166666666667</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Cohen's Kappa</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Agg R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0.4859669594055149</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.7001599073410034</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>f1-score</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7631191760666993</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9152941176470588</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8323081037710618</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.56973293768546</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2953846153846154</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3890577507598784</v>
+      </c>
+      <c r="E4" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.6362179487179487</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.6107692307692307</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.6232339089481946</v>
+      </c>
+      <c r="E5" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.715</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>macro avg</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.656356687490036</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6071493212669683</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6148665878263783</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>weighted avg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6937235584918681</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6909711184070174</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IoU</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Clase 0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7127805771873569</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Clase 1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2415094339622642</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Clase 2</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4526795895096921</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Cohen's Kappa</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Agg R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0.4774956457970483</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.7442057728767395</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>f1-score</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.8375527426160337</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9389782403027436</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8853702051739518</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.685064935064935</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.4762979683972912</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5619174434087882</v>
+      </c>
+      <c r="E4" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.7173913043478261</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5214446952595937</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.6039215686274509</v>
+      </c>
+      <c r="E5" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>macro avg</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7466696606762649</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6455736346532095</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6837364057367304</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>weighted avg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.7972915373167161</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7960464320232628</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IoU</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Clase 0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7943177270908364</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Clase 1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.3907407407407407</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Clase 2</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4325842696629214</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Cohen's Kappa</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Agg R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0.5367488337874219</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.6499300599098206</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>f1-score</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.84412265758092</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9375591296121097</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8883908561183326</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.4875846501128668</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5632333767926988</v>
+      </c>
+      <c r="E4" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.7042682926829268</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5214446952595937</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5992217898832685</v>
+      </c>
+      <c r="E5" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.8096666666666666</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8096666666666666</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8096666666666666</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8096666666666666</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>macro avg</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7383525389768377</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6488628249948568</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6836153409314333</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>weighted avg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.7972664950393117</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8096666666666666</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7976753028905361</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IoU</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Clase 0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7991935483870968</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Clase 1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.3920145190562613</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Clase 2</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4277777777777778</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Cohen's Kappa</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Agg R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0.5428942876996135</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.6432287096977234</v>
       </c>
     </row>
   </sheetData>

--- a/modelado/modelos/resultados/Class/ML_cla.xlsx
+++ b/modelado/modelos/resultados/Class/ML_cla.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E29"/>
+  <dimension ref="A2:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -742,17 +742,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.768±0.003</t>
+          <t>0.782±0.005</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.974±0.003</t>
+          <t>0.966±0.000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.859±0.003</t>
+          <t>0.865±0.003</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -769,17 +769,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.776±0.013</t>
+          <t>0.766±0.010</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.440±0.009</t>
+          <t>0.460±0.002</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.562±0.009</t>
+          <t>0.575±0.005</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -796,17 +796,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.856±0.012</t>
+          <t>0.854±0.003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.490±0.010</t>
+          <t>0.550±0.017</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.623±0.009</t>
+          <t>0.669±0.012</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.778±0.004</t>
+          <t>0.789±0.003</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.778±0.004</t>
+          <t>0.789±0.003</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.778±0.004</t>
+          <t>0.789±0.003</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.778±0.004</t>
+          <t>0.789±0.003</t>
         </is>
       </c>
     </row>
@@ -850,17 +850,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.800±0.006</t>
+          <t>0.801±0.003</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.635±0.006</t>
+          <t>0.659±0.005</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.681±0.006</t>
+          <t>0.703±0.003</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -877,17 +877,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.786±0.004</t>
+          <t>0.793±0.001</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.778±0.004</t>
+          <t>0.789±0.003</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.756±0.004</t>
+          <t>0.772±0.003</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.752±0.004</t>
+          <t>0.762±0.004</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.390±0.008</t>
+          <t>0.403±0.003</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.453±0.009</t>
+          <t>0.503±0.010</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0.535±0.008</t>
+          <t>0.566±0.006</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.187±0.030</t>
+          <t>nan±nan</t>
         </is>
       </c>
     </row>
@@ -978,36 +978,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.197±0.007</t>
+          <t>0.186±0.005</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MLOTST</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.150±0.006</t>
+          <t>0.113±0.007</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>MLOTST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.134±0.004</t>
+          <t>0.082±0.001</t>
         </is>
       </c>
     </row>
@@ -1019,67 +1019,127 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0.130±0.003</t>
+          <t>0.082±0.004</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>ZSD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.122±0.004</t>
+          <t>0.073±0.004</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VGO</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.109±0.002</t>
+          <t>0.072±0.002</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UGO</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0.105±0.002</t>
+          <t>0.064±0.001</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MSEN</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0.027±0.002</t>
+          <t>0.063±0.004</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>VGO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0.062±0.003</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>UGO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.059±0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TOB</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0.058±0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ZO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0.053±0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>MCOS</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>0.026±0.002</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0.019±0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MSEN</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0.016±0.000</t>
         </is>
       </c>
     </row>

--- a/modelado/modelos/resultados/Class/ML_cla.xlsx
+++ b/modelado/modelos/resultados/Class/ML_cla.xlsx
@@ -742,17 +742,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.782±0.005</t>
+          <t>0.764±0.003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.966±0.000</t>
+          <t>0.984±0.004</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.865±0.003</t>
+          <t>0.860±0.003</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -769,22 +769,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.766±0.010</t>
+          <t>0.914±0.002</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.460±0.002</t>
+          <t>0.504±0.011</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.575±0.005</t>
+          <t>0.650±0.009</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>288.000±0.000</t>
+          <t>403.000±0.000</t>
         </is>
       </c>
     </row>
@@ -796,22 +796,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.854±0.003</t>
+          <t>0.847±0.048</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.550±0.017</t>
+          <t>0.428±0.000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.669±0.012</t>
+          <t>0.568±0.011</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>288.000±0.000</t>
+          <t>173.000±0.000</t>
         </is>
       </c>
     </row>
@@ -823,22 +823,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.789±0.003</t>
+          <t>0.791±0.005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.789±0.003</t>
+          <t>0.791±0.005</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.789±0.003</t>
+          <t>0.791±0.005</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.789±0.003</t>
+          <t>0.791±0.005</t>
         </is>
       </c>
     </row>
@@ -850,17 +850,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.801±0.003</t>
+          <t>0.842±0.017</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.659±0.005</t>
+          <t>0.639±0.005</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.703±0.003</t>
+          <t>0.693±0.008</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -877,17 +877,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.793±0.001</t>
+          <t>0.814±0.008</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.789±0.003</t>
+          <t>0.791±0.005</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.772±0.003</t>
+          <t>0.770±0.006</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.762±0.004</t>
+          <t>0.755±0.003</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.403±0.003</t>
+          <t>0.481±0.007</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.503±0.010</t>
+          <t>0.397±0.007</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0.566±0.006</t>
+          <t>0.550±0.007</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -978,24 +978,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.186±0.005</t>
+          <t>0.155±0.002</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.113±0.007</t>
+          <t>0.132±0.002</t>
         </is>
       </c>
     </row>
@@ -1007,115 +1007,115 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.082±0.001</t>
+          <t>0.098±0.005</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SPM</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0.082±0.004</t>
+          <t>0.072±0.003</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ZSD</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.073±0.004</t>
+          <t>0.071±0.000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>ZSD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.072±0.002</t>
+          <t>0.070±0.002</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>ZO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0.064±0.001</t>
+          <t>0.069±0.000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0.063±0.004</t>
+          <t>0.065±0.003</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VGO</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0.062±0.003</t>
+          <t>0.062±0.000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UGO</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0.059±0.001</t>
+          <t>0.061±0.002</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TOB</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0.058±0.000</t>
+          <t>0.058±0.003</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ZO</t>
+          <t>TOB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0.053±0.001</t>
+          <t>0.050±0.002</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0.019±0.000</t>
+          <t>0.020±0.003</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0.016±0.000</t>
+          <t>0.017±0.000</t>
         </is>
       </c>
     </row>

--- a/modelado/modelos/resultados/Class/ML_cla.xlsx
+++ b/modelado/modelos/resultados/Class/ML_cla.xlsx
@@ -742,17 +742,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.764±0.003</t>
+          <t>0.767±0.000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.984±0.004</t>
+          <t>0.981±0.005</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.860±0.003</t>
+          <t>0.861±0.002</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -769,17 +769,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.914±0.002</t>
+          <t>0.900±0.007</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.504±0.011</t>
+          <t>0.524±0.007</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.650±0.009</t>
+          <t>0.662±0.004</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -796,17 +796,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.847±0.048</t>
+          <t>0.845±0.031</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.428±0.000</t>
+          <t>0.410±0.008</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.568±0.011</t>
+          <t>0.553±0.014</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.791±0.005</t>
+          <t>0.792±0.002</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.791±0.005</t>
+          <t>0.792±0.002</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.791±0.005</t>
+          <t>0.792±0.002</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.791±0.005</t>
+          <t>0.792±0.002</t>
         </is>
       </c>
     </row>
@@ -850,17 +850,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.842±0.017</t>
+          <t>0.838±0.013</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.639±0.005</t>
+          <t>0.638±0.002</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.693±0.008</t>
+          <t>0.692±0.004</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -877,17 +877,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.814±0.008</t>
+          <t>0.812±0.005</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.791±0.005</t>
+          <t>0.792±0.002</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.770±0.006</t>
+          <t>0.772±0.002</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.755±0.003</t>
+          <t>0.756±0.002</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.481±0.007</t>
+          <t>0.495±0.003</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.397±0.007</t>
+          <t>0.382±0.009</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0.550±0.007</t>
+          <t>0.555±0.002</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.155±0.002</t>
+          <t>0.151±0.001</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.132±0.002</t>
+          <t>0.136±0.004</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.098±0.005</t>
+          <t>0.094±0.002</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0.072±0.003</t>
+          <t>0.071±0.000</t>
         </is>
       </c>
     </row>
@@ -1031,43 +1031,43 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.071±0.000</t>
+          <t>0.070±0.003</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ZSD</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.070±0.002</t>
+          <t>0.068±0.003</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ZO</t>
+          <t>ZSD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0.069±0.000</t>
+          <t>0.067±0.001</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VGO</t>
+          <t>ZO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0.065±0.003</t>
+          <t>0.066±0.002</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0.062±0.000</t>
+          <t>0.064±0.002</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0.061±0.002</t>
+          <t>0.062±0.001</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0.058±0.003</t>
+          <t>0.059±0.004</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0.050±0.002</t>
+          <t>0.051±0.001</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0.020±0.003</t>
+          <t>0.019±0.001</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0.017±0.000</t>
+          <t>0.019±0.002</t>
         </is>
       </c>
     </row>
